--- a/downloads/Payroll_Ocak_2026.xlsx
+++ b/downloads/Payroll_Ocak_2026.xlsx
@@ -5,21 +5,22 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Bordro Özet" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Kesinti Yapıları" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="139">
   <si>
     <t>Sicil</t>
   </si>
   <si>
-    <t>Ad</t>
-  </si>
-  <si>
-    <t>SGK</t>
+    <t>Ad Soyad</t>
+  </si>
+  <si>
+    <t>SGK Gün</t>
   </si>
   <si>
     <t>Çalışılan</t>
@@ -28,19 +29,37 @@
     <t>Eksik</t>
   </si>
   <si>
-    <t>Brüt</t>
-  </si>
-  <si>
-    <t>Net</t>
-  </si>
-  <si>
-    <t>GV</t>
-  </si>
-  <si>
-    <t>GV İst</t>
-  </si>
-  <si>
-    <t>GV Tech</t>
+    <t>Temel Maaş</t>
+  </si>
+  <si>
+    <t>Yemek</t>
+  </si>
+  <si>
+    <t>Yol</t>
+  </si>
+  <si>
+    <t>FM</t>
+  </si>
+  <si>
+    <t>Prim</t>
+  </si>
+  <si>
+    <t>İkramiye</t>
+  </si>
+  <si>
+    <t>Masraf</t>
+  </si>
+  <si>
+    <t>Toplam Kazanç</t>
+  </si>
+  <si>
+    <t>SGK İşçi</t>
+  </si>
+  <si>
+    <t>İşsizlik İşçi</t>
+  </si>
+  <si>
+    <t>Gelir Vergisi</t>
   </si>
   <si>
     <t>Damga</t>
@@ -49,10 +68,28 @@
     <t>BES</t>
   </si>
   <si>
-    <t>Masraf</t>
-  </si>
-  <si>
-    <t>İşveren</t>
+    <t>Diğer Kesinti</t>
+  </si>
+  <si>
+    <t>Avans</t>
+  </si>
+  <si>
+    <t>Kesinti Toplamı</t>
+  </si>
+  <si>
+    <t>Net Maaş</t>
+  </si>
+  <si>
+    <t>GV Matrah</t>
+  </si>
+  <si>
+    <t>SGK Matrah</t>
+  </si>
+  <si>
+    <t>Damga Bazı</t>
+  </si>
+  <si>
+    <t>İşveren Maliyeti</t>
   </si>
   <si>
     <t>6101</t>
@@ -245,6 +282,153 @@
   </si>
   <si>
     <t>Emre Varlik</t>
+  </si>
+  <si>
+    <t>Bireysel Emeklilik (BES) Kesintisi (Tutar)</t>
+  </si>
+  <si>
+    <t>Bireysel Emeklilik (BES) Kesintisi (İstisna)</t>
+  </si>
+  <si>
+    <t>Bireysel Emeklilik (BES) Kesintisi (Matrah)</t>
+  </si>
+  <si>
+    <t>Damga Vergisi (Tutar)</t>
+  </si>
+  <si>
+    <t>Damga Vergisi (İstisna)</t>
+  </si>
+  <si>
+    <t>Damga Vergisi (Matrah)</t>
+  </si>
+  <si>
+    <t>Engellilik İndirimi (Tutar)</t>
+  </si>
+  <si>
+    <t>Engellilik İndirimi (İstisna)</t>
+  </si>
+  <si>
+    <t>Engellilik İndirimi (Matrah)</t>
+  </si>
+  <si>
+    <t>GVK63 Aylık Aşan Prim (Tutar)</t>
+  </si>
+  <si>
+    <t>GVK63 Aylık Aşan Prim (İstisna)</t>
+  </si>
+  <si>
+    <t>GVK63 Aylık Aşan Prim (Matrah)</t>
+  </si>
+  <si>
+    <t>GVK63 Yıllık Aşan Prim (Tutar)</t>
+  </si>
+  <si>
+    <t>GVK63 Yıllık Aşan Prim (İstisna)</t>
+  </si>
+  <si>
+    <t>GVK63 Yıllık Aşan Prim (Matrah)</t>
+  </si>
+  <si>
+    <t>GVK63 Ücret %15 Sınırı (Tutar)</t>
+  </si>
+  <si>
+    <t>GVK63 Ücret %15 Sınırı (İstisna)</t>
+  </si>
+  <si>
+    <t>GVK63 Ücret %15 Sınırı (Matrah)</t>
+  </si>
+  <si>
+    <t>Gelir Vergisi (Tutar)</t>
+  </si>
+  <si>
+    <t>Gelir Vergisi (İstisna)</t>
+  </si>
+  <si>
+    <t>Gelir Vergisi (Matrah)</t>
+  </si>
+  <si>
+    <t>SGK Primi İşveren Payı (Tutar)</t>
+  </si>
+  <si>
+    <t>SGK Primi İşveren Payı (İstisna)</t>
+  </si>
+  <si>
+    <t>SGK Primi İşveren Payı (Matrah)</t>
+  </si>
+  <si>
+    <t>SGK Primi İşveren Payı [%2 Puan Teşvik] (Tutar)</t>
+  </si>
+  <si>
+    <t>SGK Primi İşveren Payı [%2 Puan Teşvik] (İstisna)</t>
+  </si>
+  <si>
+    <t>SGK Primi İşveren Payı [%2 Puan Teşvik] (Matrah)</t>
+  </si>
+  <si>
+    <t>SGK Primi İşveren Payı [%5 Puan Teşvik (İmalat)] (Tutar)</t>
+  </si>
+  <si>
+    <t>SGK Primi İşveren Payı [%5 Puan Teşvik (İmalat)] (İstisna)</t>
+  </si>
+  <si>
+    <t>SGK Primi İşveren Payı [%5 Puan Teşvik (İmalat)] (Matrah)</t>
+  </si>
+  <si>
+    <t>SGK Primi İşveren Payı [05746 - İşveren %50 (genel)] (Tutar)</t>
+  </si>
+  <si>
+    <t>SGK Primi İşveren Payı [05746 - İşveren %50 (genel)] (İstisna)</t>
+  </si>
+  <si>
+    <t>SGK Primi İşveren Payı [05746 - İşveren %50 (genel)] (Matrah)</t>
+  </si>
+  <si>
+    <t>SGK Primi İşveren Payı [15746 - İşveren %50 (varyant)] (Tutar)</t>
+  </si>
+  <si>
+    <t>SGK Primi İşveren Payı [15746 - İşveren %50 (varyant)] (İstisna)</t>
+  </si>
+  <si>
+    <t>SGK Primi İşveren Payı [15746 - İşveren %50 (varyant)] (Matrah)</t>
+  </si>
+  <si>
+    <t>SGK Primi İşçi Payı (Tutar)</t>
+  </si>
+  <si>
+    <t>SGK Primi İşçi Payı (İstisna)</t>
+  </si>
+  <si>
+    <t>SGK Primi İşçi Payı (Matrah)</t>
+  </si>
+  <si>
+    <t>Sağlık+BES SGK İstisnası Kapaması (Tutar)</t>
+  </si>
+  <si>
+    <t>Sağlık+BES SGK İstisnası Kapaması (İstisna)</t>
+  </si>
+  <si>
+    <t>Sağlık+BES SGK İstisnası Kapaması (Matrah)</t>
+  </si>
+  <si>
+    <t>İşsizlik Sigortası Primi İşveren Hissesi (Tutar)</t>
+  </si>
+  <si>
+    <t>İşsizlik Sigortası Primi İşveren Hissesi (İstisna)</t>
+  </si>
+  <si>
+    <t>İşsizlik Sigortası Primi İşveren Hissesi (Matrah)</t>
+  </si>
+  <si>
+    <t>İşsizlik Sigortası Primi İşçi Payı (Tutar)</t>
+  </si>
+  <si>
+    <t>İşsizlik Sigortası Primi İşçi Payı (İstisna)</t>
+  </si>
+  <si>
+    <t>İşsizlik Sigortası Primi İşçi Payı (Matrah)</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -625,10 +809,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:Z33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="16" width="15" customWidth="1"/>
+    <col min="17" max="18" width="12" customWidth="1"/>
+    <col min="19" max="19" width="15" customWidth="1"/>
+    <col min="20" max="20" width="12" customWidth="1"/>
+    <col min="21" max="21" width="17" customWidth="1"/>
+    <col min="22" max="25" width="12" customWidth="1"/>
+    <col min="26" max="26" width="18" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -671,13 +869,49 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -689,36 +923,75 @@
         <v>0</v>
       </c>
       <c r="F2">
+        <v>50500</v>
+      </c>
+      <c r="G2">
+        <v>5500</v>
+      </c>
+      <c r="H2">
+        <v>3200</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
         <v>59200</v>
       </c>
-      <c r="G2">
-        <v>48094.64</v>
-      </c>
-      <c r="H2">
+      <c r="N2">
+        <v>7801.36</v>
+      </c>
+      <c r="O2">
+        <v>557.24</v>
+      </c>
+      <c r="P2">
         <v>2589.88</v>
       </c>
-      <c r="I2">
-        <v>4211.33</v>
-      </c>
-      <c r="K2">
-        <v>156.88</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
+      <c r="Q2">
+        <v>198.63</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>8880</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>11147.11</v>
+      </c>
+      <c r="V2">
+        <v>48052.89</v>
+      </c>
+      <c r="W2">
+        <v>45341.4</v>
+      </c>
+      <c r="X2">
+        <v>55724</v>
+      </c>
+      <c r="Y2">
+        <v>59200</v>
+      </c>
+      <c r="Z2">
         <v>72434.45</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C3">
         <v>30</v>
@@ -730,36 +1003,75 @@
         <v>0</v>
       </c>
       <c r="F3">
+        <v>53000</v>
+      </c>
+      <c r="G3">
+        <v>5500</v>
+      </c>
+      <c r="H3">
+        <v>3200</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
         <v>61700</v>
       </c>
-      <c r="G3">
-        <v>49881.91</v>
-      </c>
-      <c r="H3">
+      <c r="N3">
+        <v>8151.36</v>
+      </c>
+      <c r="O3">
+        <v>582.24</v>
+      </c>
+      <c r="P3">
         <v>2908.63</v>
       </c>
-      <c r="I3">
-        <v>4211.33</v>
-      </c>
-      <c r="K3">
-        <v>175.86</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
+      <c r="Q3">
+        <v>217.6</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>9255</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>11859.83</v>
+      </c>
+      <c r="V3">
+        <v>49840.17</v>
+      </c>
+      <c r="W3">
+        <v>47466.4</v>
+      </c>
+      <c r="X3">
+        <v>58224</v>
+      </c>
+      <c r="Y3">
+        <v>61700</v>
+      </c>
+      <c r="Z3">
         <v>74363.72</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C4">
         <v>30</v>
@@ -771,36 +1083,75 @@
         <v>0</v>
       </c>
       <c r="F4">
+        <v>55500</v>
+      </c>
+      <c r="G4">
+        <v>5500</v>
+      </c>
+      <c r="H4">
+        <v>3200</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
         <v>64200</v>
       </c>
-      <c r="G4">
-        <v>51669.19</v>
-      </c>
-      <c r="H4">
+      <c r="N4">
+        <v>8501.36</v>
+      </c>
+      <c r="O4">
+        <v>607.24</v>
+      </c>
+      <c r="P4">
         <v>3227.38</v>
       </c>
-      <c r="I4">
-        <v>4211.33</v>
-      </c>
-      <c r="K4">
-        <v>194.83</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
+      <c r="Q4">
+        <v>236.58</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>9630</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>12572.56</v>
+      </c>
+      <c r="V4">
+        <v>51627.44</v>
+      </c>
+      <c r="W4">
+        <v>49591.4</v>
+      </c>
+      <c r="X4">
+        <v>60724</v>
+      </c>
+      <c r="Y4">
+        <v>64200</v>
+      </c>
+      <c r="Z4">
         <v>75585.75</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C5">
         <v>30</v>
@@ -812,36 +1163,75 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>62601.85</v>
+        <v>53106.63</v>
       </c>
       <c r="G5">
-        <v>50700</v>
+        <v>5500</v>
       </c>
       <c r="H5">
-        <v>2858.62</v>
+        <v>3200</v>
       </c>
       <c r="I5">
-        <v>4211.33</v>
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>174.35</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>61806.63</v>
       </c>
       <c r="N5">
-        <v>76644.24</v>
+        <v>8166.29</v>
+      </c>
+      <c r="O5">
+        <v>583.31</v>
+      </c>
+      <c r="P5">
+        <v>2922.22</v>
+      </c>
+      <c r="Q5">
+        <v>218.41</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>9270.99</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>11890.23</v>
+      </c>
+      <c r="V5">
+        <v>49916.4</v>
+      </c>
+      <c r="W5">
+        <v>47557.03</v>
+      </c>
+      <c r="X5">
+        <v>58330.63</v>
+      </c>
+      <c r="Y5">
+        <v>61806.63</v>
+      </c>
+      <c r="Z5">
+        <v>75660.15</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C6">
         <v>30</v>
@@ -853,36 +1243,75 @@
         <v>0</v>
       </c>
       <c r="F6">
+        <v>60500</v>
+      </c>
+      <c r="G6">
+        <v>5500</v>
+      </c>
+      <c r="H6">
+        <v>3200</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
         <v>69200</v>
       </c>
-      <c r="G6">
-        <v>55243.74</v>
-      </c>
-      <c r="H6">
+      <c r="N6">
+        <v>9201.36</v>
+      </c>
+      <c r="O6">
+        <v>657.24</v>
+      </c>
+      <c r="P6">
         <v>3864.88</v>
       </c>
-      <c r="I6">
-        <v>4211.33</v>
-      </c>
-      <c r="K6">
-        <v>232.78</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
+      <c r="Q6">
+        <v>274.53</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>10380</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>13998.01</v>
+      </c>
+      <c r="V6">
+        <v>55201.99</v>
+      </c>
+      <c r="W6">
+        <v>53841.4</v>
+      </c>
+      <c r="X6">
+        <v>65724</v>
+      </c>
+      <c r="Y6">
+        <v>69200</v>
+      </c>
+      <c r="Z6">
         <v>77520.59</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C7">
         <v>30</v>
@@ -894,36 +1323,75 @@
         <v>0</v>
       </c>
       <c r="F7">
+        <v>48000</v>
+      </c>
+      <c r="G7">
+        <v>5500</v>
+      </c>
+      <c r="H7">
+        <v>3200</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
         <v>56700</v>
       </c>
-      <c r="G7">
-        <v>46307.36</v>
-      </c>
-      <c r="H7">
+      <c r="N7">
+        <v>7451.36</v>
+      </c>
+      <c r="O7">
+        <v>532.24</v>
+      </c>
+      <c r="P7">
         <v>2271.13</v>
       </c>
-      <c r="I7">
-        <v>4211.33</v>
-      </c>
-      <c r="K7">
-        <v>137.91</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
+      <c r="Q7">
+        <v>179.65</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>8505</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>10434.38</v>
+      </c>
+      <c r="V7">
+        <v>46265.62</v>
+      </c>
+      <c r="W7">
+        <v>43216.4</v>
+      </c>
+      <c r="X7">
+        <v>53224</v>
+      </c>
+      <c r="Y7">
+        <v>56700</v>
+      </c>
+      <c r="Z7">
         <v>62659.5</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C8">
         <v>30</v>
@@ -935,39 +1403,75 @@
         <v>0</v>
       </c>
       <c r="F8">
+        <v>50500</v>
+      </c>
+      <c r="G8">
+        <v>5500</v>
+      </c>
+      <c r="H8">
+        <v>3200</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
         <v>59200</v>
       </c>
-      <c r="G8">
+      <c r="N8">
+        <v>7801.36</v>
+      </c>
+      <c r="O8">
+        <v>557.24</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>8880</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>8358.6</v>
+      </c>
+      <c r="V8">
         <v>50841.4</v>
       </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>4211.33</v>
-      </c>
-      <c r="J8">
-        <v>2589.88</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
+      <c r="W8">
+        <v>45341.4</v>
+      </c>
+      <c r="X8">
+        <v>55724</v>
+      </c>
+      <c r="Y8">
+        <v>59200</v>
+      </c>
+      <c r="Z8">
         <v>66333.09</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C9">
         <v>30</v>
@@ -979,39 +1483,75 @@
         <v>0</v>
       </c>
       <c r="F9">
+        <v>53000</v>
+      </c>
+      <c r="G9">
+        <v>5500</v>
+      </c>
+      <c r="H9">
+        <v>3200</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
         <v>61700</v>
       </c>
-      <c r="G9">
+      <c r="N9">
+        <v>8151.36</v>
+      </c>
+      <c r="O9">
+        <v>582.24</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>9255</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>8733.6</v>
+      </c>
+      <c r="V9">
         <v>52966.4</v>
       </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>4211.33</v>
-      </c>
-      <c r="J9">
-        <v>2908.63</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
+      <c r="W9">
+        <v>47466.4</v>
+      </c>
+      <c r="X9">
+        <v>58224</v>
+      </c>
+      <c r="Y9">
+        <v>61700</v>
+      </c>
+      <c r="Z9">
         <v>69129.97</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C10">
         <v>30</v>
@@ -1023,39 +1563,75 @@
         <v>0</v>
       </c>
       <c r="F10">
+        <v>55500</v>
+      </c>
+      <c r="G10">
+        <v>5500</v>
+      </c>
+      <c r="H10">
+        <v>3200</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
         <v>64200</v>
       </c>
-      <c r="G10">
+      <c r="N10">
+        <v>8501.36</v>
+      </c>
+      <c r="O10">
+        <v>607.24</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>9630</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>9108.6</v>
+      </c>
+      <c r="V10">
         <v>55091.4</v>
       </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>4211.33</v>
-      </c>
-      <c r="J10">
-        <v>3227.38</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
+      <c r="W10">
+        <v>49591.4</v>
+      </c>
+      <c r="X10">
+        <v>60724</v>
+      </c>
+      <c r="Y10">
+        <v>64200</v>
+      </c>
+      <c r="Z10">
         <v>78621.95</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C11">
         <v>30</v>
@@ -1067,36 +1643,75 @@
         <v>0</v>
       </c>
       <c r="F11">
+        <v>42000</v>
+      </c>
+      <c r="G11">
+        <v>5500</v>
+      </c>
+      <c r="H11">
+        <v>3200</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
         <v>50700</v>
       </c>
-      <c r="G11">
-        <v>42017.9</v>
-      </c>
-      <c r="H11">
-        <v>1506.13</v>
-      </c>
-      <c r="I11">
-        <v>4211.33</v>
-      </c>
-      <c r="K11">
-        <v>92.37</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
       <c r="N11">
+        <v>3541.8</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>2037.4</v>
+      </c>
+      <c r="Q11">
+        <v>134.11</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>7605</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>5713.31</v>
+      </c>
+      <c r="V11">
+        <v>44986.69</v>
+      </c>
+      <c r="W11">
+        <v>41658.2</v>
+      </c>
+      <c r="X11">
+        <v>47224</v>
+      </c>
+      <c r="Y11">
+        <v>50700</v>
+      </c>
+      <c r="Z11">
         <v>61915.7</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C12">
         <v>30</v>
@@ -1108,36 +1723,75 @@
         <v>0</v>
       </c>
       <c r="F12">
+        <v>60500</v>
+      </c>
+      <c r="G12">
+        <v>5500</v>
+      </c>
+      <c r="H12">
+        <v>3200</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
         <v>69200</v>
       </c>
-      <c r="G12">
-        <v>55243.74</v>
-      </c>
-      <c r="H12">
-        <v>3864.88</v>
-      </c>
-      <c r="I12">
-        <v>4211.33</v>
-      </c>
-      <c r="K12">
-        <v>232.78</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
       <c r="N12">
+        <v>9201.36</v>
+      </c>
+      <c r="O12">
+        <v>657.24</v>
+      </c>
+      <c r="P12">
+        <v>2064.88</v>
+      </c>
+      <c r="Q12">
+        <v>274.53</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>22380</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>12198.01</v>
+      </c>
+      <c r="V12">
+        <v>57001.99</v>
+      </c>
+      <c r="W12">
+        <v>41841.4</v>
+      </c>
+      <c r="X12">
+        <v>65724</v>
+      </c>
+      <c r="Y12">
+        <v>69200</v>
+      </c>
+      <c r="Z12">
         <v>84809.45</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C13">
         <v>30</v>
@@ -1149,36 +1803,75 @@
         <v>0</v>
       </c>
       <c r="F13">
+        <v>48000</v>
+      </c>
+      <c r="G13">
+        <v>5500</v>
+      </c>
+      <c r="H13">
+        <v>3200</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <v>56700</v>
       </c>
-      <c r="G13">
-        <v>46307.36</v>
-      </c>
-      <c r="H13">
-        <v>2271.13</v>
-      </c>
-      <c r="I13">
-        <v>4211.33</v>
-      </c>
-      <c r="K13">
-        <v>137.91</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
       <c r="N13">
+        <v>7451.36</v>
+      </c>
+      <c r="O13">
+        <v>532.24</v>
+      </c>
+      <c r="P13">
+        <v>1221.13</v>
+      </c>
+      <c r="Q13">
+        <v>179.65</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>15505</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>9384.38</v>
+      </c>
+      <c r="V13">
+        <v>47315.62</v>
+      </c>
+      <c r="W13">
+        <v>36216.4</v>
+      </c>
+      <c r="X13">
+        <v>53224</v>
+      </c>
+      <c r="Y13">
+        <v>56700</v>
+      </c>
+      <c r="Z13">
         <v>69340.7</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C14">
         <v>30</v>
@@ -1190,36 +1883,75 @@
         <v>0</v>
       </c>
       <c r="F14">
+        <v>50500</v>
+      </c>
+      <c r="G14">
+        <v>5500</v>
+      </c>
+      <c r="H14">
+        <v>3200</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
         <v>59200</v>
       </c>
-      <c r="G14">
-        <v>48094.64</v>
-      </c>
-      <c r="H14">
-        <v>2589.88</v>
-      </c>
-      <c r="I14">
-        <v>4211.33</v>
-      </c>
-      <c r="K14">
-        <v>156.88</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
       <c r="N14">
+        <v>7801.36</v>
+      </c>
+      <c r="O14">
+        <v>557.24</v>
+      </c>
+      <c r="P14">
+        <v>2139.88</v>
+      </c>
+      <c r="Q14">
+        <v>198.63</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>11880</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>10697.11</v>
+      </c>
+      <c r="V14">
+        <v>48502.89</v>
+      </c>
+      <c r="W14">
+        <v>42341.4</v>
+      </c>
+      <c r="X14">
+        <v>55724</v>
+      </c>
+      <c r="Y14">
+        <v>59200</v>
+      </c>
+      <c r="Z14">
         <v>72434.45</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C15">
         <v>30</v>
@@ -1231,36 +1963,75 @@
         <v>4</v>
       </c>
       <c r="F15">
+        <v>38866.67</v>
+      </c>
+      <c r="G15">
+        <v>5500</v>
+      </c>
+      <c r="H15">
+        <v>3200</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
         <v>47566.67</v>
       </c>
-      <c r="G15">
-        <v>39777.85</v>
-      </c>
-      <c r="H15">
+      <c r="N15">
+        <v>6172.69</v>
+      </c>
+      <c r="O15">
+        <v>440.91</v>
+      </c>
+      <c r="P15">
         <v>1106.63</v>
       </c>
-      <c r="I15">
-        <v>4211.33</v>
-      </c>
-      <c r="K15">
-        <v>68.59</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
+      <c r="Q15">
+        <v>110.33</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>7135</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>7830.56</v>
+      </c>
+      <c r="V15">
+        <v>39736.11</v>
+      </c>
+      <c r="W15">
+        <v>35453.07</v>
+      </c>
+      <c r="X15">
+        <v>44090.67</v>
+      </c>
+      <c r="Y15">
+        <v>47566.67</v>
+      </c>
+      <c r="Z15">
         <v>58038.2</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C16">
         <v>30</v>
@@ -1275,13 +2046,16 @@
         <v>18000</v>
       </c>
       <c r="G16">
-        <v>15300</v>
+        <v>0</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>4211.33</v>
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -1290,18 +2064,54 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>2700</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>18000</v>
+      </c>
+      <c r="W16">
+        <v>18000</v>
+      </c>
+      <c r="X16">
+        <v>18000</v>
+      </c>
+      <c r="Y16">
+        <v>18000</v>
+      </c>
+      <c r="Z16">
         <v>22275</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C17">
         <v>30</v>
@@ -1313,36 +2123,75 @@
         <v>0</v>
       </c>
       <c r="F17">
+        <v>58000</v>
+      </c>
+      <c r="G17">
+        <v>5500</v>
+      </c>
+      <c r="H17">
+        <v>3200</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
         <v>66700</v>
       </c>
-      <c r="G17">
-        <v>53456.46</v>
-      </c>
-      <c r="H17">
+      <c r="N17">
+        <v>8851.36</v>
+      </c>
+      <c r="O17">
+        <v>632.24</v>
+      </c>
+      <c r="P17">
         <v>3546.13</v>
       </c>
-      <c r="I17">
-        <v>4211.33</v>
-      </c>
-      <c r="K17">
-        <v>213.81</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
+      <c r="Q17">
+        <v>255.55</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>10005</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>13285.28</v>
+      </c>
+      <c r="V17">
+        <v>53414.72</v>
+      </c>
+      <c r="W17">
+        <v>51716.4</v>
+      </c>
+      <c r="X17">
+        <v>63224</v>
+      </c>
+      <c r="Y17">
+        <v>66700</v>
+      </c>
+      <c r="Z17">
         <v>81715.7</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C18">
         <v>30</v>
@@ -1354,36 +2203,75 @@
         <v>0</v>
       </c>
       <c r="F18">
+        <v>60500</v>
+      </c>
+      <c r="G18">
+        <v>5500</v>
+      </c>
+      <c r="H18">
+        <v>3200</v>
+      </c>
+      <c r="I18">
+        <v>4840</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
         <v>74040</v>
       </c>
-      <c r="G18">
-        <v>58703.9</v>
-      </c>
-      <c r="H18">
+      <c r="N18">
+        <v>9878.96</v>
+      </c>
+      <c r="O18">
+        <v>705.64</v>
+      </c>
+      <c r="P18">
         <v>4481.98</v>
       </c>
-      <c r="I18">
-        <v>4211.33</v>
-      </c>
-      <c r="K18">
-        <v>269.52</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
+      <c r="Q18">
+        <v>311.26</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>11106</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>15377.84</v>
+      </c>
+      <c r="V18">
+        <v>58662.16</v>
+      </c>
+      <c r="W18">
+        <v>57955.4</v>
+      </c>
+      <c r="X18">
+        <v>70564</v>
+      </c>
+      <c r="Y18">
+        <v>74040</v>
+      </c>
+      <c r="Z18">
         <v>90798.95</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C19">
         <v>30</v>
@@ -1395,36 +2283,75 @@
         <v>0</v>
       </c>
       <c r="F19">
+        <v>48000</v>
+      </c>
+      <c r="G19">
+        <v>5500</v>
+      </c>
+      <c r="H19">
+        <v>3200</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
         <v>56700</v>
       </c>
-      <c r="G19">
-        <v>39107.36</v>
-      </c>
-      <c r="H19">
+      <c r="N19">
+        <v>7451.36</v>
+      </c>
+      <c r="O19">
+        <v>532.24</v>
+      </c>
+      <c r="P19">
         <v>2271.13</v>
       </c>
-      <c r="I19">
-        <v>4211.33</v>
-      </c>
-      <c r="K19">
-        <v>137.91</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
+      <c r="Q19">
+        <v>179.65</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>8505</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>10434.38</v>
+      </c>
+      <c r="V19">
+        <v>46265.62</v>
+      </c>
+      <c r="W19">
+        <v>43216.4</v>
+      </c>
+      <c r="X19">
+        <v>53224</v>
+      </c>
+      <c r="Y19">
+        <v>56700</v>
+      </c>
+      <c r="Z19">
         <v>69340.7</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C20">
         <v>30</v>
@@ -1436,36 +2363,75 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>64200</v>
+        <v>50500</v>
       </c>
       <c r="G20">
-        <v>51669.19</v>
+        <v>5500</v>
       </c>
       <c r="H20">
-        <v>3227.38</v>
+        <v>3200</v>
       </c>
       <c r="I20">
-        <v>4211.33</v>
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>194.83</v>
+        <v>0</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>59200</v>
       </c>
       <c r="N20">
-        <v>78621.95</v>
+        <v>7801.36</v>
+      </c>
+      <c r="O20">
+        <v>557.24</v>
+      </c>
+      <c r="P20">
+        <v>2589.88</v>
+      </c>
+      <c r="Q20">
+        <v>198.63</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>8880</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>11147.11</v>
+      </c>
+      <c r="V20">
+        <v>48052.89</v>
+      </c>
+      <c r="W20">
+        <v>45341.4</v>
+      </c>
+      <c r="X20">
+        <v>55724</v>
+      </c>
+      <c r="Y20">
+        <v>59200</v>
+      </c>
+      <c r="Z20">
+        <v>72434.45</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C21">
         <v>30</v>
@@ -1477,36 +2443,75 @@
         <v>0</v>
       </c>
       <c r="F21">
+        <v>53000</v>
+      </c>
+      <c r="G21">
+        <v>5500</v>
+      </c>
+      <c r="H21">
+        <v>3200</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
         <v>61700</v>
       </c>
-      <c r="G21">
-        <v>48681.91</v>
-      </c>
-      <c r="H21">
+      <c r="N21">
+        <v>8151.36</v>
+      </c>
+      <c r="O21">
+        <v>582.24</v>
+      </c>
+      <c r="P21">
         <v>2908.63</v>
       </c>
-      <c r="I21">
-        <v>4211.33</v>
-      </c>
-      <c r="K21">
-        <v>175.86</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
+      <c r="Q21">
+        <v>217.6</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>9255</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>11859.83</v>
+      </c>
+      <c r="V21">
+        <v>49840.17</v>
+      </c>
+      <c r="W21">
+        <v>47466.4</v>
+      </c>
+      <c r="X21">
+        <v>58224</v>
+      </c>
+      <c r="Y21">
+        <v>61700</v>
+      </c>
+      <c r="Z21">
         <v>75528.2</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -1518,36 +2523,75 @@
         <v>0</v>
       </c>
       <c r="F22">
+        <v>55500</v>
+      </c>
+      <c r="G22">
+        <v>5500</v>
+      </c>
+      <c r="H22">
+        <v>3200</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
         <v>64200</v>
       </c>
-      <c r="G22">
-        <v>51669.19</v>
-      </c>
-      <c r="H22">
+      <c r="N22">
+        <v>8501.36</v>
+      </c>
+      <c r="O22">
+        <v>607.24</v>
+      </c>
+      <c r="P22">
         <v>3227.38</v>
       </c>
-      <c r="I22">
-        <v>4211.33</v>
-      </c>
-      <c r="K22">
-        <v>194.83</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
+      <c r="Q22">
+        <v>236.58</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>9630</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>12572.56</v>
+      </c>
+      <c r="V22">
+        <v>51627.44</v>
+      </c>
+      <c r="W22">
+        <v>49591.4</v>
+      </c>
+      <c r="X22">
+        <v>60724</v>
+      </c>
+      <c r="Y22">
+        <v>64200</v>
+      </c>
+      <c r="Z22">
         <v>78621.95</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C23">
         <v>30</v>
@@ -1559,36 +2603,75 @@
         <v>0</v>
       </c>
       <c r="F23">
+        <v>58000</v>
+      </c>
+      <c r="G23">
+        <v>5500</v>
+      </c>
+      <c r="H23">
+        <v>3200</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
         <v>68440</v>
       </c>
-      <c r="G23">
-        <v>51546.54</v>
-      </c>
-      <c r="H23">
+      <c r="N23">
+        <v>8851.36</v>
+      </c>
+      <c r="O23">
+        <v>632.24</v>
+      </c>
+      <c r="P23">
         <v>3546.13</v>
       </c>
-      <c r="I23">
-        <v>4211.33</v>
-      </c>
-      <c r="K23">
-        <v>227.01</v>
-      </c>
-      <c r="L23">
+      <c r="Q23">
+        <v>268.76</v>
+      </c>
+      <c r="R23">
         <v>1896.72</v>
       </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
+      <c r="S23">
+        <v>10266</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>15195.21</v>
+      </c>
+      <c r="V23">
+        <v>51504.79</v>
+      </c>
+      <c r="W23">
+        <v>51716.4</v>
+      </c>
+      <c r="X23">
+        <v>63224</v>
+      </c>
+      <c r="Y23">
+        <v>68440</v>
+      </c>
+      <c r="Z23">
         <v>83455.7</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C24">
         <v>30</v>
@@ -1600,36 +2683,75 @@
         <v>0</v>
       </c>
       <c r="F24">
+        <v>60500</v>
+      </c>
+      <c r="G24">
+        <v>5500</v>
+      </c>
+      <c r="H24">
+        <v>3200</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
         <v>69200</v>
       </c>
-      <c r="G24">
-        <v>52801.67</v>
-      </c>
-      <c r="H24">
+      <c r="N24">
+        <v>9201.36</v>
+      </c>
+      <c r="O24">
+        <v>657.24</v>
+      </c>
+      <c r="P24">
         <v>6306.95</v>
       </c>
-      <c r="I24">
-        <v>4211.33</v>
-      </c>
-      <c r="K24">
-        <v>232.78</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24">
+      <c r="Q24">
+        <v>274.53</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>10380</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>16440.08</v>
+      </c>
+      <c r="V24">
+        <v>52759.92</v>
+      </c>
+      <c r="W24">
+        <v>53841.4</v>
+      </c>
+      <c r="X24">
+        <v>65724</v>
+      </c>
+      <c r="Y24">
+        <v>69200</v>
+      </c>
+      <c r="Z24">
         <v>84809.45</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C25">
         <v>30</v>
@@ -1641,36 +2763,75 @@
         <v>0</v>
       </c>
       <c r="F25">
+        <v>26008</v>
+      </c>
+      <c r="G25">
+        <v>5500</v>
+      </c>
+      <c r="H25">
+        <v>3200</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
         <v>34708</v>
       </c>
-      <c r="G25">
-        <v>30023.2</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>4211.33</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
       <c r="N25">
+        <v>4372.48</v>
+      </c>
+      <c r="O25">
+        <v>312.32</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>12.73</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>5206.2</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>4697.53</v>
+      </c>
+      <c r="V25">
+        <v>30010.47</v>
+      </c>
+      <c r="W25">
+        <v>24523.2</v>
+      </c>
+      <c r="X25">
+        <v>31232</v>
+      </c>
+      <c r="Y25">
+        <v>34708</v>
+      </c>
+      <c r="Z25">
         <v>42125.6</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C26">
         <v>30</v>
@@ -1682,36 +2843,75 @@
         <v>0</v>
       </c>
       <c r="F26">
+        <v>50500</v>
+      </c>
+      <c r="G26">
+        <v>5500</v>
+      </c>
+      <c r="H26">
+        <v>3200</v>
+      </c>
+      <c r="I26">
+        <v>4040</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
         <v>63240</v>
       </c>
-      <c r="G26">
-        <v>50982.87</v>
-      </c>
-      <c r="H26">
+      <c r="N26">
+        <v>8366.96</v>
+      </c>
+      <c r="O26">
+        <v>597.64</v>
+      </c>
+      <c r="P26">
         <v>3104.98</v>
       </c>
-      <c r="I26">
-        <v>4211.33</v>
-      </c>
-      <c r="K26">
-        <v>187.55</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26">
+      <c r="Q26">
+        <v>229.29</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>9486</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>12298.87</v>
+      </c>
+      <c r="V26">
+        <v>50941.13</v>
+      </c>
+      <c r="W26">
+        <v>48775.4</v>
+      </c>
+      <c r="X26">
+        <v>59764</v>
+      </c>
+      <c r="Y26">
+        <v>63240</v>
+      </c>
+      <c r="Z26">
         <v>71251.79</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C27">
         <v>30</v>
@@ -1723,36 +2923,75 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>54200</v>
+        <v>42000</v>
       </c>
       <c r="G27">
-        <v>44520.09</v>
+        <v>5500</v>
       </c>
       <c r="H27">
-        <v>1952.38</v>
+        <v>3200</v>
       </c>
       <c r="I27">
-        <v>4211.33</v>
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
       </c>
       <c r="K27">
-        <v>118.93</v>
+        <v>0</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>50700</v>
       </c>
       <c r="N27">
-        <v>66246.95</v>
+        <v>3541.8</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>2037.4</v>
+      </c>
+      <c r="Q27">
+        <v>134.11</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>7605</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>5713.31</v>
+      </c>
+      <c r="V27">
+        <v>44986.69</v>
+      </c>
+      <c r="W27">
+        <v>41658.2</v>
+      </c>
+      <c r="X27">
+        <v>47224</v>
+      </c>
+      <c r="Y27">
+        <v>50700</v>
+      </c>
+      <c r="Z27">
+        <v>61915.7</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C28">
         <v>30</v>
@@ -1764,36 +3003,75 @@
         <v>0</v>
       </c>
       <c r="F28">
+        <v>55500</v>
+      </c>
+      <c r="G28">
+        <v>5500</v>
+      </c>
+      <c r="H28">
+        <v>3200</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
         <v>64200</v>
       </c>
-      <c r="G28">
-        <v>50869.19</v>
-      </c>
-      <c r="H28">
-        <v>3227.38</v>
-      </c>
-      <c r="I28">
-        <v>4211.33</v>
-      </c>
-      <c r="K28">
-        <v>194.83</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
       <c r="N28">
+        <v>8501.36</v>
+      </c>
+      <c r="O28">
+        <v>607.24</v>
+      </c>
+      <c r="P28">
+        <v>2177.38</v>
+      </c>
+      <c r="Q28">
+        <v>236.58</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>16630</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>11522.56</v>
+      </c>
+      <c r="V28">
+        <v>52677.44</v>
+      </c>
+      <c r="W28">
+        <v>42591.4</v>
+      </c>
+      <c r="X28">
+        <v>60724</v>
+      </c>
+      <c r="Y28">
+        <v>64200</v>
+      </c>
+      <c r="Z28">
         <v>78621.95</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="C29">
         <v>30</v>
@@ -1805,36 +3083,75 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>76700</v>
+        <v>58000</v>
       </c>
       <c r="G29">
-        <v>60605.56</v>
+        <v>5500</v>
       </c>
       <c r="H29">
-        <v>4821.13</v>
+        <v>3200</v>
       </c>
       <c r="I29">
-        <v>4211.33</v>
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>289.71</v>
+        <v>0</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>66700</v>
       </c>
       <c r="N29">
-        <v>94090.7</v>
+        <v>8851.36</v>
+      </c>
+      <c r="O29">
+        <v>632.24</v>
+      </c>
+      <c r="P29">
+        <v>3546.13</v>
+      </c>
+      <c r="Q29">
+        <v>255.55</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>10005</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>13285.28</v>
+      </c>
+      <c r="V29">
+        <v>53414.72</v>
+      </c>
+      <c r="W29">
+        <v>51716.4</v>
+      </c>
+      <c r="X29">
+        <v>63224</v>
+      </c>
+      <c r="Y29">
+        <v>66700</v>
+      </c>
+      <c r="Z29">
+        <v>81715.7</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C30">
         <v>30</v>
@@ -1846,36 +3163,75 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>65200</v>
+        <v>52000</v>
       </c>
       <c r="G30">
-        <v>52384.1</v>
+        <v>5500</v>
       </c>
       <c r="H30">
-        <v>3354.88</v>
+        <v>3200</v>
       </c>
       <c r="I30">
-        <v>4211.33</v>
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
       </c>
       <c r="K30">
-        <v>202.42</v>
+        <v>0</v>
       </c>
       <c r="L30">
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>60700</v>
       </c>
       <c r="N30">
-        <v>78624.97</v>
+        <v>8011.36</v>
+      </c>
+      <c r="O30">
+        <v>572.24</v>
+      </c>
+      <c r="P30">
+        <v>2781.13</v>
+      </c>
+      <c r="Q30">
+        <v>210.01</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>9105</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>11574.74</v>
+      </c>
+      <c r="V30">
+        <v>49125.26</v>
+      </c>
+      <c r="W30">
+        <v>46616.4</v>
+      </c>
+      <c r="X30">
+        <v>57224</v>
+      </c>
+      <c r="Y30">
+        <v>60700</v>
+      </c>
+      <c r="Z30">
+        <v>73146.22</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C31">
         <v>30</v>
@@ -1887,36 +3243,75 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>67301.74</v>
+        <v>53524.56</v>
       </c>
       <c r="G31">
-        <v>54060</v>
+        <v>5500</v>
       </c>
       <c r="H31">
-        <v>3457.85</v>
+        <v>3200</v>
       </c>
       <c r="I31">
-        <v>4211.33</v>
+        <v>4281.96</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>210.03</v>
+        <v>0</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>66506.52</v>
       </c>
       <c r="N31">
-        <v>82460.35</v>
+        <v>8824.27</v>
+      </c>
+      <c r="O31">
+        <v>630.31</v>
+      </c>
+      <c r="P31">
+        <v>3521.46</v>
+      </c>
+      <c r="Q31">
+        <v>254.08</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>9975.98</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>13230.12</v>
+      </c>
+      <c r="V31">
+        <v>53276.4</v>
+      </c>
+      <c r="W31">
+        <v>51551.94</v>
+      </c>
+      <c r="X31">
+        <v>63030.52</v>
+      </c>
+      <c r="Y31">
+        <v>66506.52</v>
+      </c>
+      <c r="Z31">
+        <v>81476.27</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C32">
         <v>30</v>
@@ -1928,36 +3323,75 @@
         <v>0</v>
       </c>
       <c r="F32">
+        <v>58000</v>
+      </c>
+      <c r="G32">
+        <v>5500</v>
+      </c>
+      <c r="H32">
+        <v>3200</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
         <v>66700</v>
       </c>
-      <c r="G32">
-        <v>53456.46</v>
-      </c>
-      <c r="H32">
+      <c r="N32">
+        <v>8851.36</v>
+      </c>
+      <c r="O32">
+        <v>632.24</v>
+      </c>
+      <c r="P32">
         <v>3546.13</v>
       </c>
-      <c r="I32">
-        <v>4211.33</v>
-      </c>
-      <c r="K32">
-        <v>213.81</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
+      <c r="Q32">
+        <v>255.55</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>10005</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>13285.28</v>
+      </c>
+      <c r="V32">
+        <v>53414.72</v>
+      </c>
+      <c r="W32">
+        <v>51716.4</v>
+      </c>
+      <c r="X32">
+        <v>63224</v>
+      </c>
+      <c r="Y32">
+        <v>66700</v>
+      </c>
+      <c r="Z32">
         <v>81715.7</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="C33">
         <v>30</v>
@@ -1969,28 +3403,5124 @@
         <v>0</v>
       </c>
       <c r="F33">
+        <v>54000</v>
+      </c>
+      <c r="G33">
+        <v>5500</v>
+      </c>
+      <c r="H33">
+        <v>3200</v>
+      </c>
+      <c r="I33">
+        <v>4320</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
         <v>67020</v>
       </c>
+      <c r="N33">
+        <v>8896.16</v>
+      </c>
+      <c r="O33">
+        <v>635.44</v>
+      </c>
+      <c r="P33">
+        <v>3586.93</v>
+      </c>
+      <c r="Q33">
+        <v>257.98</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>10053</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>13376.51</v>
+      </c>
+      <c r="V33">
+        <v>53643.49</v>
+      </c>
+      <c r="W33">
+        <v>51988.4</v>
+      </c>
+      <c r="X33">
+        <v>63544</v>
+      </c>
+      <c r="Y33">
+        <v>67020</v>
+      </c>
+      <c r="Z33">
+        <v>78934.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AX33"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="5" width="42" customWidth="1"/>
+    <col min="6" max="6" width="23" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="29" customWidth="1"/>
+    <col min="10" max="10" width="31" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="12" max="12" width="31" customWidth="1"/>
+    <col min="13" max="13" width="33" customWidth="1"/>
+    <col min="14" max="15" width="32" customWidth="1"/>
+    <col min="16" max="16" width="34" customWidth="1"/>
+    <col min="17" max="17" width="33" customWidth="1"/>
+    <col min="18" max="18" width="32" customWidth="1"/>
+    <col min="19" max="19" width="34" customWidth="1"/>
+    <col min="20" max="20" width="33" customWidth="1"/>
+    <col min="21" max="21" width="23" customWidth="1"/>
+    <col min="22" max="22" width="25" customWidth="1"/>
+    <col min="23" max="23" width="24" customWidth="1"/>
+    <col min="24" max="24" width="32" customWidth="1"/>
+    <col min="25" max="25" width="34" customWidth="1"/>
+    <col min="26" max="26" width="33" customWidth="1"/>
+    <col min="27" max="38" width="42" customWidth="1"/>
+    <col min="39" max="39" width="29" customWidth="1"/>
+    <col min="40" max="40" width="31" customWidth="1"/>
+    <col min="41" max="41" width="30" customWidth="1"/>
+    <col min="42" max="50" width="42" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:50" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E2">
+        <v>55724</v>
+      </c>
+      <c r="F2">
+        <v>198.63</v>
+      </c>
+      <c r="G2">
+        <v>250.7</v>
+      </c>
+      <c r="H2">
+        <v>59200</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
+        <v>138</v>
+      </c>
+      <c r="K2" t="s">
+        <v>138</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2" t="s">
+        <v>138</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>8880</v>
+      </c>
+      <c r="S2" t="s">
+        <v>138</v>
+      </c>
+      <c r="T2">
+        <v>59200</v>
+      </c>
+      <c r="U2">
+        <v>2589.88</v>
+      </c>
+      <c r="V2">
+        <v>4211.33</v>
+      </c>
+      <c r="W2">
+        <v>45341.4</v>
+      </c>
+      <c r="X2">
+        <v>12119.97</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z2">
+        <v>55724</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM2">
+        <v>7801.36</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO2">
+        <v>55724</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>1114.48</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU2">
+        <v>55724</v>
+      </c>
+      <c r="AV2">
+        <v>557.24</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX2">
+        <v>55724</v>
+      </c>
+    </row>
+    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3">
+        <v>58224</v>
+      </c>
+      <c r="F3">
+        <v>217.6</v>
+      </c>
+      <c r="G3">
+        <v>250.7</v>
+      </c>
+      <c r="H3">
+        <v>61700</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3" t="s">
+        <v>138</v>
+      </c>
+      <c r="K3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3" t="s">
+        <v>138</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>9255</v>
+      </c>
+      <c r="S3" t="s">
+        <v>138</v>
+      </c>
+      <c r="T3">
+        <v>61700</v>
+      </c>
+      <c r="U3">
+        <v>2908.63</v>
+      </c>
+      <c r="V3">
+        <v>4211.33</v>
+      </c>
+      <c r="W3">
+        <v>47466.4</v>
+      </c>
+      <c r="X3">
+        <v>12663.72</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z3">
+        <v>58224</v>
+      </c>
+      <c r="AA3">
+        <v>-1164.48</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC3">
+        <v>58224</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM3">
+        <v>8151.36</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO3">
+        <v>58224</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>1164.48</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU3">
+        <v>58224</v>
+      </c>
+      <c r="AV3">
+        <v>582.24</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX3">
+        <v>58224</v>
+      </c>
+    </row>
+    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E4">
+        <v>60724</v>
+      </c>
+      <c r="F4">
+        <v>236.58</v>
+      </c>
+      <c r="G4">
+        <v>250.7</v>
+      </c>
+      <c r="H4">
+        <v>64200</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4" t="s">
+        <v>138</v>
+      </c>
+      <c r="K4" t="s">
+        <v>138</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4" t="s">
+        <v>138</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>9630</v>
+      </c>
+      <c r="S4" t="s">
+        <v>138</v>
+      </c>
+      <c r="T4">
+        <v>64200</v>
+      </c>
+      <c r="U4">
+        <v>3227.38</v>
+      </c>
+      <c r="V4">
+        <v>4211.33</v>
+      </c>
+      <c r="W4">
+        <v>49591.4</v>
+      </c>
+      <c r="X4">
+        <v>13207.47</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z4">
+        <v>60724</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD4">
+        <v>-3036.2</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF4">
+        <v>60724</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM4">
+        <v>8501.36</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO4">
+        <v>60724</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>1214.48</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU4">
+        <v>60724</v>
+      </c>
+      <c r="AV4">
+        <v>607.24</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX4">
+        <v>60724</v>
+      </c>
+    </row>
+    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E5">
+        <v>58330.63</v>
+      </c>
+      <c r="F5">
+        <v>218.41</v>
+      </c>
+      <c r="G5">
+        <v>250.7</v>
+      </c>
+      <c r="H5">
+        <v>61806.63</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5" t="s">
+        <v>138</v>
+      </c>
+      <c r="K5" t="s">
+        <v>138</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
+        <v>138</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>9270.99</v>
+      </c>
+      <c r="S5" t="s">
+        <v>138</v>
+      </c>
+      <c r="T5">
+        <v>61806.63</v>
+      </c>
+      <c r="U5">
+        <v>2922.22</v>
+      </c>
+      <c r="V5">
+        <v>4211.33</v>
+      </c>
+      <c r="W5">
+        <v>47557.03</v>
+      </c>
+      <c r="X5">
+        <v>12686.91</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z5">
+        <v>58330.63</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM5">
+        <v>8166.29</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO5">
+        <v>58330.63</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>1166.61</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU5">
+        <v>58330.63</v>
+      </c>
+      <c r="AV5">
+        <v>583.31</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX5">
+        <v>58330.63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E6">
+        <v>65724</v>
+      </c>
+      <c r="F6">
+        <v>274.53</v>
+      </c>
+      <c r="G6">
+        <v>250.7</v>
+      </c>
+      <c r="H6">
+        <v>69200</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6" t="s">
+        <v>138</v>
+      </c>
+      <c r="K6" t="s">
+        <v>138</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6" t="s">
+        <v>138</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>10380</v>
+      </c>
+      <c r="S6" t="s">
+        <v>138</v>
+      </c>
+      <c r="T6">
+        <v>69200</v>
+      </c>
+      <c r="U6">
+        <v>3864.88</v>
+      </c>
+      <c r="V6">
+        <v>4211.33</v>
+      </c>
+      <c r="W6">
+        <v>53841.4</v>
+      </c>
+      <c r="X6">
+        <v>14294.97</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z6">
+        <v>65724</v>
+      </c>
+      <c r="AA6">
+        <v>-1314.48</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC6">
+        <v>65724</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG6">
+        <v>-5974.38</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI6">
+        <v>65724</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM6">
+        <v>9201.36</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO6">
+        <v>65724</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>1314.48</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU6">
+        <v>65724</v>
+      </c>
+      <c r="AV6">
+        <v>657.24</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX6">
+        <v>65724</v>
+      </c>
+    </row>
+    <row r="7" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7">
+        <v>53224</v>
+      </c>
+      <c r="F7">
+        <v>179.65</v>
+      </c>
+      <c r="G7">
+        <v>250.7</v>
+      </c>
+      <c r="H7">
+        <v>56700</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
+        <v>138</v>
+      </c>
+      <c r="K7" t="s">
+        <v>138</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="s">
+        <v>138</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>8505</v>
+      </c>
+      <c r="S7" t="s">
+        <v>138</v>
+      </c>
+      <c r="T7">
+        <v>56700</v>
+      </c>
+      <c r="U7">
+        <v>2271.13</v>
+      </c>
+      <c r="V7">
+        <v>4211.33</v>
+      </c>
+      <c r="W7">
+        <v>43216.4</v>
+      </c>
+      <c r="X7">
+        <v>11576.22</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z7">
+        <v>53224</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD7">
+        <v>-2661.2</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF7">
+        <v>53224</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ7">
+        <v>-4020</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL7">
+        <v>53224</v>
+      </c>
+      <c r="AM7">
+        <v>7451.36</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO7">
+        <v>53224</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>1064.48</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU7">
+        <v>53224</v>
+      </c>
+      <c r="AV7">
+        <v>532.24</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX7">
+        <v>53224</v>
+      </c>
+    </row>
+    <row r="8" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E8">
+        <v>55724</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>250.7</v>
+      </c>
+      <c r="H8">
+        <v>59200</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>138</v>
+      </c>
+      <c r="K8" t="s">
+        <v>138</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" t="s">
+        <v>138</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>8880</v>
+      </c>
+      <c r="S8" t="s">
+        <v>138</v>
+      </c>
+      <c r="T8">
+        <v>59200</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>4211.33</v>
+      </c>
+      <c r="W8">
+        <v>45341.4</v>
+      </c>
+      <c r="X8">
+        <v>12119.97</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z8">
+        <v>55724</v>
+      </c>
+      <c r="AA8">
+        <v>-1114.48</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC8">
+        <v>55724</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG8">
+        <v>-4986.88</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI8">
+        <v>55724</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM8">
+        <v>7801.36</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO8">
+        <v>55724</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>1114.48</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU8">
+        <v>55724</v>
+      </c>
+      <c r="AV8">
+        <v>557.24</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX8">
+        <v>55724</v>
+      </c>
+    </row>
+    <row r="9" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E9">
+        <v>58224</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>250.7</v>
+      </c>
+      <c r="H9">
+        <v>61700</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>138</v>
+      </c>
+      <c r="K9" t="s">
+        <v>138</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9" t="s">
+        <v>138</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>9255</v>
+      </c>
+      <c r="S9" t="s">
+        <v>138</v>
+      </c>
+      <c r="T9">
+        <v>61700</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>4211.33</v>
+      </c>
+      <c r="W9">
+        <v>47466.4</v>
+      </c>
+      <c r="X9">
+        <v>12663.72</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z9">
+        <v>58224</v>
+      </c>
+      <c r="AA9">
+        <v>-1164.48</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC9">
+        <v>58224</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG9">
+        <v>-5233.75</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI9">
+        <v>58224</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM9">
+        <v>8151.36</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO9">
+        <v>58224</v>
+      </c>
+      <c r="AP9">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>1164.48</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU9">
+        <v>58224</v>
+      </c>
+      <c r="AV9">
+        <v>582.24</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX9">
+        <v>58224</v>
+      </c>
+    </row>
+    <row r="10" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E10">
+        <v>60724</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>250.7</v>
+      </c>
+      <c r="H10">
+        <v>64200</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10" t="s">
+        <v>138</v>
+      </c>
+      <c r="K10" t="s">
+        <v>138</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10" t="s">
+        <v>138</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>9630</v>
+      </c>
+      <c r="S10" t="s">
+        <v>138</v>
+      </c>
+      <c r="T10">
+        <v>64200</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>4211.33</v>
+      </c>
+      <c r="W10">
+        <v>49591.4</v>
+      </c>
+      <c r="X10">
+        <v>13207.47</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z10">
+        <v>60724</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM10">
+        <v>8501.36</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO10">
+        <v>60724</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>1214.48</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU10">
+        <v>60724</v>
+      </c>
+      <c r="AV10">
+        <v>607.24</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX10">
+        <v>60724</v>
+      </c>
+    </row>
+    <row r="11" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E11">
+        <v>47224</v>
+      </c>
+      <c r="F11">
+        <v>134.11</v>
+      </c>
+      <c r="G11">
+        <v>250.7</v>
+      </c>
+      <c r="H11">
+        <v>50700</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
+        <v>138</v>
+      </c>
+      <c r="K11" t="s">
+        <v>138</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" t="s">
+        <v>138</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>7605</v>
+      </c>
+      <c r="S11" t="s">
+        <v>138</v>
+      </c>
+      <c r="T11">
+        <v>50700</v>
+      </c>
+      <c r="U11">
+        <v>2037.4</v>
+      </c>
+      <c r="V11">
+        <v>4211.33</v>
+      </c>
+      <c r="W11">
+        <v>41658.2</v>
+      </c>
+      <c r="X11">
+        <v>10271.22</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z11">
+        <v>47224</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM11">
+        <v>3541.8</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO11">
+        <v>47224</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>944.48</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU11">
+        <v>47224</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX11">
+        <v>47224</v>
+      </c>
+    </row>
+    <row r="12" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>138</v>
+      </c>
+      <c r="E12">
+        <v>65724</v>
+      </c>
+      <c r="F12">
+        <v>274.53</v>
+      </c>
+      <c r="G12">
+        <v>250.7</v>
+      </c>
+      <c r="H12">
+        <v>69200</v>
+      </c>
+      <c r="I12">
+        <v>12000</v>
+      </c>
+      <c r="J12" t="s">
+        <v>138</v>
+      </c>
+      <c r="K12">
+        <v>69200</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="s">
+        <v>138</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>10380</v>
+      </c>
+      <c r="S12" t="s">
+        <v>138</v>
+      </c>
+      <c r="T12">
+        <v>69200</v>
+      </c>
+      <c r="U12">
+        <v>2064.88</v>
+      </c>
+      <c r="V12">
+        <v>4211.33</v>
+      </c>
+      <c r="W12">
+        <v>41841.4</v>
+      </c>
+      <c r="X12">
+        <v>14294.97</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z12">
+        <v>65724</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM12">
+        <v>9201.36</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO12">
+        <v>65724</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>1314.48</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU12">
+        <v>65724</v>
+      </c>
+      <c r="AV12">
+        <v>657.24</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX12">
+        <v>65724</v>
+      </c>
+    </row>
+    <row r="13" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13" t="s">
+        <v>138</v>
+      </c>
+      <c r="E13">
+        <v>53224</v>
+      </c>
+      <c r="F13">
+        <v>179.65</v>
+      </c>
+      <c r="G13">
+        <v>250.7</v>
+      </c>
+      <c r="H13">
+        <v>56700</v>
+      </c>
+      <c r="I13">
+        <v>7000</v>
+      </c>
+      <c r="J13" t="s">
+        <v>138</v>
+      </c>
+      <c r="K13">
+        <v>56700</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" t="s">
+        <v>138</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>8505</v>
+      </c>
+      <c r="S13" t="s">
+        <v>138</v>
+      </c>
+      <c r="T13">
+        <v>56700</v>
+      </c>
+      <c r="U13">
+        <v>1221.13</v>
+      </c>
+      <c r="V13">
+        <v>4211.33</v>
+      </c>
+      <c r="W13">
+        <v>36216.4</v>
+      </c>
+      <c r="X13">
+        <v>11576.22</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z13">
+        <v>53224</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM13">
+        <v>7451.36</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO13">
+        <v>53224</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>1064.48</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU13">
+        <v>53224</v>
+      </c>
+      <c r="AV13">
+        <v>532.24</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX13">
+        <v>53224</v>
+      </c>
+    </row>
+    <row r="14" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E14">
+        <v>55724</v>
+      </c>
+      <c r="F14">
+        <v>198.63</v>
+      </c>
+      <c r="G14">
+        <v>250.7</v>
+      </c>
+      <c r="H14">
+        <v>59200</v>
+      </c>
+      <c r="I14">
+        <v>3000</v>
+      </c>
+      <c r="J14" t="s">
+        <v>138</v>
+      </c>
+      <c r="K14">
+        <v>59200</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" t="s">
+        <v>138</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>8880</v>
+      </c>
+      <c r="S14" t="s">
+        <v>138</v>
+      </c>
+      <c r="T14">
+        <v>59200</v>
+      </c>
+      <c r="U14">
+        <v>2139.88</v>
+      </c>
+      <c r="V14">
+        <v>4211.33</v>
+      </c>
+      <c r="W14">
+        <v>42341.4</v>
+      </c>
+      <c r="X14">
+        <v>12119.97</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z14">
+        <v>55724</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM14">
+        <v>7801.36</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO14">
+        <v>55724</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>1114.48</v>
+      </c>
+      <c r="AT14" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU14">
+        <v>55724</v>
+      </c>
+      <c r="AV14">
+        <v>557.24</v>
+      </c>
+      <c r="AW14" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX14">
+        <v>55724</v>
+      </c>
+    </row>
+    <row r="15" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
+        <v>138</v>
+      </c>
+      <c r="E15">
+        <v>44090.67</v>
+      </c>
+      <c r="F15">
+        <v>110.33</v>
+      </c>
+      <c r="G15">
+        <v>250.7</v>
+      </c>
+      <c r="H15">
+        <v>47566.67</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15" t="s">
+        <v>138</v>
+      </c>
+      <c r="K15" t="s">
+        <v>138</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15" t="s">
+        <v>138</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>7135</v>
+      </c>
+      <c r="S15" t="s">
+        <v>138</v>
+      </c>
+      <c r="T15">
+        <v>47566.67</v>
+      </c>
+      <c r="U15">
+        <v>1106.63</v>
+      </c>
+      <c r="V15">
+        <v>4211.33</v>
+      </c>
+      <c r="W15">
+        <v>35453.07</v>
+      </c>
+      <c r="X15">
+        <v>9589.72</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z15">
+        <v>44090.67</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM15">
+        <v>6172.69</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO15">
+        <v>44090.67</v>
+      </c>
+      <c r="AP15">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>881.81</v>
+      </c>
+      <c r="AT15" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU15">
+        <v>44090.67</v>
+      </c>
+      <c r="AV15">
+        <v>440.91</v>
+      </c>
+      <c r="AW15" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX15">
+        <v>44090.67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16" t="s">
+        <v>138</v>
+      </c>
+      <c r="E16">
+        <v>18000</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>250.7</v>
+      </c>
+      <c r="H16">
+        <v>18000</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16" t="s">
+        <v>138</v>
+      </c>
+      <c r="K16" t="s">
+        <v>138</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16" t="s">
+        <v>138</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>2700</v>
+      </c>
+      <c r="S16" t="s">
+        <v>138</v>
+      </c>
+      <c r="T16">
+        <v>18000</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>4211.33</v>
+      </c>
+      <c r="W16">
+        <v>18000</v>
+      </c>
+      <c r="X16">
+        <v>3915</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z16">
+        <v>18000</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO16">
+        <v>18000</v>
+      </c>
+      <c r="AP16">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>360</v>
+      </c>
+      <c r="AT16" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU16">
+        <v>18000</v>
+      </c>
+      <c r="AV16">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX16">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17" t="s">
+        <v>138</v>
+      </c>
+      <c r="E17">
+        <v>63224</v>
+      </c>
+      <c r="F17">
+        <v>255.55</v>
+      </c>
+      <c r="G17">
+        <v>250.7</v>
+      </c>
+      <c r="H17">
+        <v>66700</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17" t="s">
+        <v>138</v>
+      </c>
+      <c r="K17" t="s">
+        <v>138</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" t="s">
+        <v>138</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>10005</v>
+      </c>
+      <c r="S17" t="s">
+        <v>138</v>
+      </c>
+      <c r="T17">
+        <v>66700</v>
+      </c>
+      <c r="U17">
+        <v>3546.13</v>
+      </c>
+      <c r="V17">
+        <v>4211.33</v>
+      </c>
+      <c r="W17">
+        <v>51716.4</v>
+      </c>
+      <c r="X17">
+        <v>13751.22</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z17">
+        <v>63224</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM17">
+        <v>8851.36</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO17">
+        <v>63224</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>1264.48</v>
+      </c>
+      <c r="AT17" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU17">
+        <v>63224</v>
+      </c>
+      <c r="AV17">
+        <v>632.24</v>
+      </c>
+      <c r="AW17" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX17">
+        <v>63224</v>
+      </c>
+    </row>
+    <row r="18" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18">
+        <v>70564</v>
+      </c>
+      <c r="F18">
+        <v>311.26</v>
+      </c>
+      <c r="G18">
+        <v>250.7</v>
+      </c>
+      <c r="H18">
+        <v>74040</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18" t="s">
+        <v>138</v>
+      </c>
+      <c r="K18" t="s">
+        <v>138</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" t="s">
+        <v>138</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>11106</v>
+      </c>
+      <c r="S18" t="s">
+        <v>138</v>
+      </c>
+      <c r="T18">
+        <v>74040</v>
+      </c>
+      <c r="U18">
+        <v>4481.98</v>
+      </c>
+      <c r="V18">
+        <v>4211.33</v>
+      </c>
+      <c r="W18">
+        <v>57955.4</v>
+      </c>
+      <c r="X18">
+        <v>15347.67</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z18">
+        <v>70564</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM18">
+        <v>9878.96</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO18">
+        <v>70564</v>
+      </c>
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>1411.28</v>
+      </c>
+      <c r="AT18" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU18">
+        <v>70564</v>
+      </c>
+      <c r="AV18">
+        <v>705.64</v>
+      </c>
+      <c r="AW18" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX18">
+        <v>70564</v>
+      </c>
+    </row>
+    <row r="19" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19" t="s">
+        <v>138</v>
+      </c>
+      <c r="E19">
+        <v>53224</v>
+      </c>
+      <c r="F19">
+        <v>179.65</v>
+      </c>
+      <c r="G19">
+        <v>250.7</v>
+      </c>
+      <c r="H19">
+        <v>56700</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19" t="s">
+        <v>138</v>
+      </c>
+      <c r="K19" t="s">
+        <v>138</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="s">
+        <v>138</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>8505</v>
+      </c>
+      <c r="S19" t="s">
+        <v>138</v>
+      </c>
+      <c r="T19">
+        <v>56700</v>
+      </c>
+      <c r="U19">
+        <v>2271.13</v>
+      </c>
+      <c r="V19">
+        <v>4211.33</v>
+      </c>
+      <c r="W19">
+        <v>43216.4</v>
+      </c>
+      <c r="X19">
+        <v>11576.22</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z19">
+        <v>53224</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM19">
+        <v>7451.36</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO19">
+        <v>53224</v>
+      </c>
+      <c r="AP19">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>1064.48</v>
+      </c>
+      <c r="AT19" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU19">
+        <v>53224</v>
+      </c>
+      <c r="AV19">
+        <v>532.24</v>
+      </c>
+      <c r="AW19" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX19">
+        <v>53224</v>
+      </c>
+    </row>
+    <row r="20" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20" t="s">
+        <v>138</v>
+      </c>
+      <c r="E20">
+        <v>55724</v>
+      </c>
+      <c r="F20">
+        <v>198.63</v>
+      </c>
+      <c r="G20">
+        <v>250.7</v>
+      </c>
+      <c r="H20">
+        <v>59200</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20" t="s">
+        <v>138</v>
+      </c>
+      <c r="K20" t="s">
+        <v>138</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="s">
+        <v>138</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>8880</v>
+      </c>
+      <c r="S20" t="s">
+        <v>138</v>
+      </c>
+      <c r="T20">
+        <v>59200</v>
+      </c>
+      <c r="U20">
+        <v>2589.88</v>
+      </c>
+      <c r="V20">
+        <v>4211.33</v>
+      </c>
+      <c r="W20">
+        <v>45341.4</v>
+      </c>
+      <c r="X20">
+        <v>12119.97</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z20">
+        <v>55724</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM20">
+        <v>7801.36</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO20">
+        <v>55724</v>
+      </c>
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>1114.48</v>
+      </c>
+      <c r="AT20" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU20">
+        <v>55724</v>
+      </c>
+      <c r="AV20">
+        <v>557.24</v>
+      </c>
+      <c r="AW20" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX20">
+        <v>55724</v>
+      </c>
+    </row>
+    <row r="21" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21" t="s">
+        <v>138</v>
+      </c>
+      <c r="E21">
+        <v>58224</v>
+      </c>
+      <c r="F21">
+        <v>217.6</v>
+      </c>
+      <c r="G21">
+        <v>250.7</v>
+      </c>
+      <c r="H21">
+        <v>61700</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21" t="s">
+        <v>138</v>
+      </c>
+      <c r="K21" t="s">
+        <v>138</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" t="s">
+        <v>138</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>9255</v>
+      </c>
+      <c r="S21" t="s">
+        <v>138</v>
+      </c>
+      <c r="T21">
+        <v>61700</v>
+      </c>
+      <c r="U21">
+        <v>2908.63</v>
+      </c>
+      <c r="V21">
+        <v>4211.33</v>
+      </c>
+      <c r="W21">
+        <v>47466.4</v>
+      </c>
+      <c r="X21">
+        <v>12663.72</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z21">
+        <v>58224</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM21">
+        <v>8151.36</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO21">
+        <v>58224</v>
+      </c>
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>1164.48</v>
+      </c>
+      <c r="AT21" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU21">
+        <v>58224</v>
+      </c>
+      <c r="AV21">
+        <v>582.24</v>
+      </c>
+      <c r="AW21" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX21">
+        <v>58224</v>
+      </c>
+    </row>
+    <row r="22" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22" t="s">
+        <v>138</v>
+      </c>
+      <c r="E22">
+        <v>60724</v>
+      </c>
+      <c r="F22">
+        <v>236.58</v>
+      </c>
+      <c r="G22">
+        <v>250.7</v>
+      </c>
+      <c r="H22">
+        <v>64200</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22" t="s">
+        <v>138</v>
+      </c>
+      <c r="K22" t="s">
+        <v>138</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" t="s">
+        <v>138</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>9630</v>
+      </c>
+      <c r="S22" t="s">
+        <v>138</v>
+      </c>
+      <c r="T22">
+        <v>64200</v>
+      </c>
+      <c r="U22">
+        <v>3227.38</v>
+      </c>
+      <c r="V22">
+        <v>4211.33</v>
+      </c>
+      <c r="W22">
+        <v>49591.4</v>
+      </c>
+      <c r="X22">
+        <v>13207.47</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z22">
+        <v>60724</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM22">
+        <v>8501.36</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO22">
+        <v>60724</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>1214.48</v>
+      </c>
+      <c r="AT22" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU22">
+        <v>60724</v>
+      </c>
+      <c r="AV22">
+        <v>607.24</v>
+      </c>
+      <c r="AW22" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX22">
+        <v>60724</v>
+      </c>
+    </row>
+    <row r="23" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23">
+        <v>1896.72</v>
+      </c>
+      <c r="D23" t="s">
+        <v>138</v>
+      </c>
+      <c r="E23">
+        <v>63224</v>
+      </c>
+      <c r="F23">
+        <v>268.76</v>
+      </c>
+      <c r="G23">
+        <v>250.7</v>
+      </c>
+      <c r="H23">
+        <v>68440</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23" t="s">
+        <v>138</v>
+      </c>
+      <c r="K23" t="s">
+        <v>138</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" t="s">
+        <v>138</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q23">
+        <v>1740</v>
+      </c>
+      <c r="R23">
+        <v>10266</v>
+      </c>
+      <c r="S23" t="s">
+        <v>138</v>
+      </c>
+      <c r="T23">
+        <v>68440</v>
+      </c>
+      <c r="U23">
+        <v>3546.13</v>
+      </c>
+      <c r="V23">
+        <v>4211.33</v>
+      </c>
+      <c r="W23">
+        <v>51716.4</v>
+      </c>
+      <c r="X23">
+        <v>13751.22</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z23">
+        <v>63224</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF23" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL23" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM23">
+        <v>8851.36</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO23">
+        <v>63224</v>
+      </c>
+      <c r="AP23">
+        <v>1740</v>
+      </c>
+      <c r="AQ23" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR23">
+        <v>1740</v>
+      </c>
+      <c r="AS23">
+        <v>1264.48</v>
+      </c>
+      <c r="AT23" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU23">
+        <v>63224</v>
+      </c>
+      <c r="AV23">
+        <v>632.24</v>
+      </c>
+      <c r="AW23" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX23">
+        <v>63224</v>
+      </c>
+    </row>
+    <row r="24" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24" t="s">
+        <v>138</v>
+      </c>
+      <c r="E24">
+        <v>65724</v>
+      </c>
+      <c r="F24">
+        <v>274.53</v>
+      </c>
+      <c r="G24">
+        <v>250.7</v>
+      </c>
+      <c r="H24">
+        <v>69200</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24" t="s">
+        <v>138</v>
+      </c>
+      <c r="K24" t="s">
+        <v>138</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24" t="s">
+        <v>138</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>10380</v>
+      </c>
+      <c r="S24" t="s">
+        <v>138</v>
+      </c>
+      <c r="T24">
+        <v>69200</v>
+      </c>
+      <c r="U24">
+        <v>6306.95</v>
+      </c>
+      <c r="V24">
+        <v>4211.33</v>
+      </c>
+      <c r="W24">
+        <v>53841.4</v>
+      </c>
+      <c r="X24">
+        <v>14294.97</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z24">
+        <v>65724</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM24">
+        <v>9201.36</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO24">
+        <v>65724</v>
+      </c>
+      <c r="AP24">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>1314.48</v>
+      </c>
+      <c r="AT24" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU24">
+        <v>65724</v>
+      </c>
+      <c r="AV24">
+        <v>657.24</v>
+      </c>
+      <c r="AW24" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX24">
+        <v>65724</v>
+      </c>
+    </row>
+    <row r="25" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="s">
+        <v>138</v>
+      </c>
+      <c r="E25">
+        <v>31232</v>
+      </c>
+      <c r="F25">
+        <v>12.73</v>
+      </c>
+      <c r="G25">
+        <v>250.7</v>
+      </c>
+      <c r="H25">
+        <v>34708</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25" t="s">
+        <v>138</v>
+      </c>
+      <c r="K25" t="s">
+        <v>138</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" t="s">
+        <v>138</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>5206.2</v>
+      </c>
+      <c r="S25" t="s">
+        <v>138</v>
+      </c>
+      <c r="T25">
+        <v>34708</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>4211.33</v>
+      </c>
+      <c r="W25">
+        <v>24523.2</v>
+      </c>
+      <c r="X25">
+        <v>6792.96</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z25">
+        <v>31232</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF25" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL25" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM25">
+        <v>4372.48</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO25">
+        <v>31232</v>
+      </c>
+      <c r="AP25">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>624.64</v>
+      </c>
+      <c r="AT25" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU25">
+        <v>31232</v>
+      </c>
+      <c r="AV25">
+        <v>312.32</v>
+      </c>
+      <c r="AW25" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX25">
+        <v>31232</v>
+      </c>
+    </row>
+    <row r="26" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26" t="s">
+        <v>138</v>
+      </c>
+      <c r="E26">
+        <v>59764</v>
+      </c>
+      <c r="F26">
+        <v>229.29</v>
+      </c>
+      <c r="G26">
+        <v>250.7</v>
+      </c>
+      <c r="H26">
+        <v>63240</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26" t="s">
+        <v>138</v>
+      </c>
+      <c r="K26" t="s">
+        <v>138</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="s">
+        <v>138</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>9486</v>
+      </c>
+      <c r="S26" t="s">
+        <v>138</v>
+      </c>
+      <c r="T26">
+        <v>63240</v>
+      </c>
+      <c r="U26">
+        <v>3104.98</v>
+      </c>
+      <c r="V26">
+        <v>4211.33</v>
+      </c>
+      <c r="W26">
+        <v>48775.4</v>
+      </c>
+      <c r="X26">
+        <v>12998.67</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z26">
+        <v>59764</v>
+      </c>
+      <c r="AA26">
+        <v>-1195.28</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC26">
+        <v>59764</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF26" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG26">
+        <v>-4986.88</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI26">
+        <v>59764</v>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM26">
+        <v>8366.96</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO26">
+        <v>59764</v>
+      </c>
+      <c r="AP26">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>1195.28</v>
+      </c>
+      <c r="AT26" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU26">
+        <v>59764</v>
+      </c>
+      <c r="AV26">
+        <v>597.64</v>
+      </c>
+      <c r="AW26" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX26">
+        <v>59764</v>
+      </c>
+    </row>
+    <row r="27" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27" t="s">
+        <v>138</v>
+      </c>
+      <c r="E27">
+        <v>47224</v>
+      </c>
+      <c r="F27">
+        <v>134.11</v>
+      </c>
+      <c r="G27">
+        <v>250.7</v>
+      </c>
+      <c r="H27">
+        <v>50700</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27" t="s">
+        <v>138</v>
+      </c>
+      <c r="K27" t="s">
+        <v>138</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="s">
+        <v>138</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>7605</v>
+      </c>
+      <c r="S27" t="s">
+        <v>138</v>
+      </c>
+      <c r="T27">
+        <v>50700</v>
+      </c>
+      <c r="U27">
+        <v>2037.4</v>
+      </c>
+      <c r="V27">
+        <v>4211.33</v>
+      </c>
+      <c r="W27">
+        <v>41658.2</v>
+      </c>
+      <c r="X27">
+        <v>10271.22</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z27">
+        <v>47224</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF27" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI27" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL27" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM27">
+        <v>3541.8</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO27">
+        <v>47224</v>
+      </c>
+      <c r="AP27">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>944.48</v>
+      </c>
+      <c r="AT27" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU27">
+        <v>47224</v>
+      </c>
+      <c r="AV27">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX27">
+        <v>47224</v>
+      </c>
+    </row>
+    <row r="28" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>78</v>
+      </c>
+      <c r="B28" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28">
+        <v>60724</v>
+      </c>
+      <c r="F28">
+        <v>236.58</v>
+      </c>
+      <c r="G28">
+        <v>250.7</v>
+      </c>
+      <c r="H28">
+        <v>64200</v>
+      </c>
+      <c r="I28">
+        <v>7000</v>
+      </c>
+      <c r="J28" t="s">
+        <v>138</v>
+      </c>
+      <c r="K28">
+        <v>64200</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" t="s">
+        <v>138</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>9630</v>
+      </c>
+      <c r="S28" t="s">
+        <v>138</v>
+      </c>
+      <c r="T28">
+        <v>64200</v>
+      </c>
+      <c r="U28">
+        <v>2177.38</v>
+      </c>
+      <c r="V28">
+        <v>4211.33</v>
+      </c>
+      <c r="W28">
+        <v>42591.4</v>
+      </c>
+      <c r="X28">
+        <v>13207.47</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z28">
+        <v>60724</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF28" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI28" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL28" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM28">
+        <v>8501.36</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO28">
+        <v>60724</v>
+      </c>
+      <c r="AP28">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>1214.48</v>
+      </c>
+      <c r="AT28" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU28">
+        <v>60724</v>
+      </c>
+      <c r="AV28">
+        <v>607.24</v>
+      </c>
+      <c r="AW28" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX28">
+        <v>60724</v>
+      </c>
+    </row>
+    <row r="29" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29" t="s">
+        <v>138</v>
+      </c>
+      <c r="E29">
+        <v>63224</v>
+      </c>
+      <c r="F29">
+        <v>255.55</v>
+      </c>
+      <c r="G29">
+        <v>250.7</v>
+      </c>
+      <c r="H29">
+        <v>66700</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29" t="s">
+        <v>138</v>
+      </c>
+      <c r="K29" t="s">
+        <v>138</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29" t="s">
+        <v>138</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>10005</v>
+      </c>
+      <c r="S29" t="s">
+        <v>138</v>
+      </c>
+      <c r="T29">
+        <v>66700</v>
+      </c>
+      <c r="U29">
+        <v>3546.13</v>
+      </c>
+      <c r="V29">
+        <v>4211.33</v>
+      </c>
+      <c r="W29">
+        <v>51716.4</v>
+      </c>
+      <c r="X29">
+        <v>13751.22</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z29">
+        <v>63224</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF29" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM29">
+        <v>8851.36</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO29">
+        <v>63224</v>
+      </c>
+      <c r="AP29">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>1264.48</v>
+      </c>
+      <c r="AT29" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU29">
+        <v>63224</v>
+      </c>
+      <c r="AV29">
+        <v>632.24</v>
+      </c>
+      <c r="AW29" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX29">
+        <v>63224</v>
+      </c>
+    </row>
+    <row r="30" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30" t="s">
+        <v>138</v>
+      </c>
+      <c r="E30">
+        <v>57224</v>
+      </c>
+      <c r="F30">
+        <v>210.01</v>
+      </c>
+      <c r="G30">
+        <v>250.7</v>
+      </c>
+      <c r="H30">
+        <v>60700</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30" t="s">
+        <v>138</v>
+      </c>
+      <c r="K30" t="s">
+        <v>138</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30" t="s">
+        <v>138</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>9105</v>
+      </c>
+      <c r="S30" t="s">
+        <v>138</v>
+      </c>
+      <c r="T30">
+        <v>60700</v>
+      </c>
+      <c r="U30">
+        <v>2781.13</v>
+      </c>
+      <c r="V30">
+        <v>4211.33</v>
+      </c>
+      <c r="W30">
+        <v>46616.4</v>
+      </c>
+      <c r="X30">
+        <v>12446.22</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z30">
+        <v>57224</v>
+      </c>
+      <c r="AA30">
+        <v>-1144.48</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC30">
+        <v>57224</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF30" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI30" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ30">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM30">
+        <v>8011.36</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO30">
+        <v>57224</v>
+      </c>
+      <c r="AP30">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>1144.48</v>
+      </c>
+      <c r="AT30" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU30">
+        <v>57224</v>
+      </c>
+      <c r="AV30">
+        <v>572.24</v>
+      </c>
+      <c r="AW30" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX30">
+        <v>57224</v>
+      </c>
+    </row>
+    <row r="31" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31" t="s">
+        <v>138</v>
+      </c>
+      <c r="E31">
+        <v>63030.52</v>
+      </c>
+      <c r="F31">
+        <v>254.08</v>
+      </c>
+      <c r="G31">
+        <v>250.7</v>
+      </c>
+      <c r="H31">
+        <v>66506.52</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31" t="s">
+        <v>138</v>
+      </c>
+      <c r="K31" t="s">
+        <v>138</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" t="s">
+        <v>138</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>9975.98</v>
+      </c>
+      <c r="S31" t="s">
+        <v>138</v>
+      </c>
+      <c r="T31">
+        <v>66506.52</v>
+      </c>
+      <c r="U31">
+        <v>3521.46</v>
+      </c>
+      <c r="V31">
+        <v>4211.33</v>
+      </c>
+      <c r="W31">
+        <v>51551.94</v>
+      </c>
+      <c r="X31">
+        <v>13709.14</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z31">
+        <v>63030.52</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF31" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI31" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ31">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM31">
+        <v>8824.27</v>
+      </c>
+      <c r="AN31" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO31">
+        <v>63030.52</v>
+      </c>
+      <c r="AP31">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>1260.61</v>
+      </c>
+      <c r="AT31" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU31">
+        <v>63030.52</v>
+      </c>
+      <c r="AV31">
+        <v>630.31</v>
+      </c>
+      <c r="AW31" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX31">
+        <v>63030.52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>86</v>
+      </c>
+      <c r="B32" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32" t="s">
+        <v>138</v>
+      </c>
+      <c r="E32">
+        <v>63224</v>
+      </c>
+      <c r="F32">
+        <v>255.55</v>
+      </c>
+      <c r="G32">
+        <v>250.7</v>
+      </c>
+      <c r="H32">
+        <v>66700</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32" t="s">
+        <v>138</v>
+      </c>
+      <c r="K32" t="s">
+        <v>138</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" t="s">
+        <v>138</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>10005</v>
+      </c>
+      <c r="S32" t="s">
+        <v>138</v>
+      </c>
+      <c r="T32">
+        <v>66700</v>
+      </c>
+      <c r="U32">
+        <v>3546.13</v>
+      </c>
+      <c r="V32">
+        <v>4211.33</v>
+      </c>
+      <c r="W32">
+        <v>51716.4</v>
+      </c>
+      <c r="X32">
+        <v>13751.22</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z32">
+        <v>63224</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF32" t="s">
+        <v>138</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI32" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM32">
+        <v>8851.36</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO32">
+        <v>63224</v>
+      </c>
+      <c r="AP32">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>1264.48</v>
+      </c>
+      <c r="AT32" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU32">
+        <v>63224</v>
+      </c>
+      <c r="AV32">
+        <v>632.24</v>
+      </c>
+      <c r="AW32" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX32">
+        <v>63224</v>
+      </c>
+    </row>
+    <row r="33" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33" t="s">
+        <v>138</v>
+      </c>
+      <c r="E33">
+        <v>63544</v>
+      </c>
+      <c r="F33">
+        <v>257.98</v>
+      </c>
       <c r="G33">
-        <v>53685.23</v>
+        <v>250.7</v>
       </c>
       <c r="H33">
+        <v>67020</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33" t="s">
+        <v>138</v>
+      </c>
+      <c r="K33" t="s">
+        <v>138</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" t="s">
+        <v>138</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>10053</v>
+      </c>
+      <c r="S33" t="s">
+        <v>138</v>
+      </c>
+      <c r="T33">
+        <v>67020</v>
+      </c>
+      <c r="U33">
         <v>3586.93</v>
       </c>
-      <c r="I33">
+      <c r="V33">
         <v>4211.33</v>
       </c>
-      <c r="K33">
-        <v>216.24</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>78934.5</v>
+      <c r="W33">
+        <v>51988.4</v>
+      </c>
+      <c r="X33">
+        <v>13820.82</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z33">
+        <v>63544</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>138</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD33">
+        <v>-3177.2</v>
+      </c>
+      <c r="AE33" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF33">
+        <v>63544</v>
+      </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI33" t="s">
+        <v>138</v>
+      </c>
+      <c r="AJ33">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>138</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>138</v>
+      </c>
+      <c r="AM33">
+        <v>8896.16</v>
+      </c>
+      <c r="AN33" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO33">
+        <v>63544</v>
+      </c>
+      <c r="AP33">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="s">
+        <v>138</v>
+      </c>
+      <c r="AR33">
+        <v>0</v>
+      </c>
+      <c r="AS33">
+        <v>1270.88</v>
+      </c>
+      <c r="AT33" t="s">
+        <v>138</v>
+      </c>
+      <c r="AU33">
+        <v>63544</v>
+      </c>
+      <c r="AV33">
+        <v>635.44</v>
+      </c>
+      <c r="AW33" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX33">
+        <v>63544</v>
       </c>
     </row>
   </sheetData>
